--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.087</t>
-  </si>
-  <si>
-    <t>(0.155)</t>
-  </si>
-  <si>
-    <t>6.645</t>
-  </si>
-  <si>
-    <t>(0.921)</t>
-  </si>
-  <si>
-    <t>2.924</t>
-  </si>
-  <si>
-    <t>(0.842)</t>
-  </si>
-  <si>
-    <t>15.350</t>
-  </si>
-  <si>
-    <t>(4.780)</t>
-  </si>
-  <si>
-    <t>1.549</t>
-  </si>
-  <si>
-    <t>(0.195)</t>
-  </si>
-  <si>
-    <t>9.513</t>
-  </si>
-  <si>
-    <t>(1.136)</t>
-  </si>
-  <si>
-    <t>4.685</t>
-  </si>
-  <si>
-    <t>(1.120)</t>
-  </si>
-  <si>
-    <t>5.105</t>
-  </si>
-  <si>
-    <t>(4.694)</t>
-  </si>
-  <si>
-    <t>22.237</t>
-  </si>
-  <si>
-    <t>(10.069)</t>
-  </si>
-  <si>
-    <t>9.285</t>
-  </si>
-  <si>
-    <t>(1.490)</t>
+    <t>1.180</t>
+  </si>
+  <si>
+    <t>(0.164)</t>
+  </si>
+  <si>
+    <t>7.214</t>
+  </si>
+  <si>
+    <t>(0.970)</t>
+  </si>
+  <si>
+    <t>2.308</t>
+  </si>
+  <si>
+    <t>(0.426)</t>
+  </si>
+  <si>
+    <t>8.545</t>
+  </si>
+  <si>
+    <t>(0.978)</t>
+  </si>
+  <si>
+    <t>1.667</t>
+  </si>
+  <si>
+    <t>(0.205)</t>
+  </si>
+  <si>
+    <t>10.300</t>
+  </si>
+  <si>
+    <t>(1.187)</t>
+  </si>
+  <si>
+    <t>2.949</t>
+  </si>
+  <si>
+    <t>(0.670)</t>
+  </si>
+  <si>
+    <t>0.441</t>
+  </si>
+  <si>
+    <t>(0.079)</t>
+  </si>
+  <si>
+    <t>10.238</t>
+  </si>
+  <si>
+    <t>(1.123)</t>
+  </si>
+  <si>
+    <t>6.943</t>
+  </si>
+  <si>
+    <t>(0.935)</t>
   </si>
   <si>
     <t>40</t>
@@ -198,7 +198,7 @@
     <t>(2.089)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>0.380</t>
-  </si>
-  <si>
-    <t>1.184</t>
-  </si>
-  <si>
-    <t>-4.903</t>
-  </si>
-  <si>
-    <t>-0.017</t>
-  </si>
-  <si>
-    <t>0.137</t>
-  </si>
-  <si>
-    <t>-1.304</t>
-  </si>
-  <si>
-    <t>-4.822</t>
-  </si>
-  <si>
-    <t>-10.392</t>
-  </si>
-  <si>
-    <t>0.475</t>
+    <t>-0.037</t>
+  </si>
+  <si>
+    <t>-0.189</t>
+  </si>
+  <si>
+    <t>1.800**</t>
+  </si>
+  <si>
+    <t>1.901</t>
+  </si>
+  <si>
+    <t>-0.135</t>
+  </si>
+  <si>
+    <t>-0.650</t>
+  </si>
+  <si>
+    <t>0.432</t>
+  </si>
+  <si>
+    <t>-0.158</t>
+  </si>
+  <si>
+    <t>1.607</t>
+  </si>
+  <si>
+    <t>2.818</t>
   </si>
 </sst>
 </file>
